--- a/INSTANCES/instances_literature_xlsx/A_MTN_1/354FL_8A_9.xlsx
+++ b/INSTANCES/instances_literature_xlsx/A_MTN_1/354FL_8A_9.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="87">
   <si>
     <t xml:space="preserve">YEAR</t>
   </si>
@@ -227,6 +227,63 @@
   </si>
   <si>
     <t>TK_DAY</t>
+  </si>
+  <si>
+    <t>TAIL_NUMBER</t>
+  </si>
+  <si>
+    <t>INIT_AIRPORT</t>
+  </si>
+  <si>
+    <t>INIT_FLYING_TIME</t>
+  </si>
+  <si>
+    <t>INIT_TAKEOFF</t>
+  </si>
+  <si>
+    <t>INIT_FLYING_DAY</t>
+  </si>
+  <si>
+    <t>N121</t>
+  </si>
+  <si>
+    <t>SAW</t>
+  </si>
+  <si>
+    <t>N122</t>
+  </si>
+  <si>
+    <t>HTY</t>
+  </si>
+  <si>
+    <t>N123</t>
+  </si>
+  <si>
+    <t>MLX</t>
+  </si>
+  <si>
+    <t>N124</t>
+  </si>
+  <si>
+    <t>ESB</t>
+  </si>
+  <si>
+    <t>N125</t>
+  </si>
+  <si>
+    <t>N126</t>
+  </si>
+  <si>
+    <t>ECN</t>
+  </si>
+  <si>
+    <t>N127</t>
+  </si>
+  <si>
+    <t>YEI</t>
+  </si>
+  <si>
+    <t>N128</t>
   </si>
 </sst>
 </file>
@@ -450,7 +507,7 @@
   <dimension ref="A1:H355"/>
   <sheetFormatPr defaultColWidth="10.62109375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="1" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A1" t="s" s="1">
         <v>0</v>
       </c>
@@ -476,7 +533,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="2" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A2" t="n" s="1">
         <v>2011</v>
       </c>
@@ -502,7 +559,7 @@
         <v>31980</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="3" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A3" t="n" s="1">
         <v>2011</v>
       </c>
@@ -528,7 +585,7 @@
         <v>31990</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="4" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A4" t="n" s="1">
         <v>2011</v>
       </c>
@@ -554,7 +611,7 @@
         <v>31980</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="5" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A5" t="n" s="1">
         <v>2011</v>
       </c>
@@ -580,7 +637,7 @@
         <v>31995</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="6" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A6" t="n" s="1">
         <v>2011</v>
       </c>
@@ -606,7 +663,7 @@
         <v>31995</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="7" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A7" t="n" s="1">
         <v>2011</v>
       </c>
@@ -632,7 +689,7 @@
         <v>32040</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="8" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A8" t="n" s="1">
         <v>2011</v>
       </c>
@@ -658,7 +715,7 @@
         <v>32075</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="9" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A9" t="n" s="1">
         <v>2011</v>
       </c>
@@ -684,7 +741,7 @@
         <v>32100</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="10" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A10" t="n" s="1">
         <v>2011</v>
       </c>
@@ -710,7 +767,7 @@
         <v>32120</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="11" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A11" t="n" s="1">
         <v>2011</v>
       </c>
@@ -736,7 +793,7 @@
         <v>32145</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="12" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A12" t="n" s="1">
         <v>2011</v>
       </c>
@@ -762,7 +819,7 @@
         <v>32155</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="13" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A13" t="n" s="1">
         <v>2011</v>
       </c>
@@ -788,7 +845,7 @@
         <v>32220</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="14" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A14" t="n" s="1">
         <v>2011</v>
       </c>
@@ -814,7 +871,7 @@
         <v>32245</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="15" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A15" t="n" s="1">
         <v>2011</v>
       </c>
@@ -840,7 +897,7 @@
         <v>32235</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="16" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A16" t="n" s="1">
         <v>2011</v>
       </c>
@@ -866,7 +923,7 @@
         <v>32220</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="17" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A17" t="n" s="1">
         <v>2011</v>
       </c>
@@ -892,7 +949,7 @@
         <v>32285</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="18" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A18" t="n" s="1">
         <v>2011</v>
       </c>
@@ -918,7 +975,7 @@
         <v>32285</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="19" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A19" t="n" s="1">
         <v>2011</v>
       </c>
@@ -944,7 +1001,7 @@
         <v>32360</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="20" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A20" t="n" s="1">
         <v>2011</v>
       </c>
@@ -970,7 +1027,7 @@
         <v>32385</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="21" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A21" t="n" s="1">
         <v>2011</v>
       </c>
@@ -996,7 +1053,7 @@
         <v>32340</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="22" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A22" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1022,7 +1079,7 @@
         <v>32425</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="23" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A23" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1048,7 +1105,7 @@
         <v>32410</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="24" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A24" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1074,7 +1131,7 @@
         <v>32450</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="25" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A25" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1100,7 +1157,7 @@
         <v>32450</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="26" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A26" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1126,7 +1183,7 @@
         <v>32450</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="27" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A27" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1152,7 +1209,7 @@
         <v>32460</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="28" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A28" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1178,7 +1235,7 @@
         <v>32555</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="29" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A29" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1204,7 +1261,7 @@
         <v>32565</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="30" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A30" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1230,7 +1287,7 @@
         <v>32565</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="31" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A31" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1256,7 +1313,7 @@
         <v>32570</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="32" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A32" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1282,7 +1339,7 @@
         <v>32555</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="33" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A33" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1308,7 +1365,7 @@
         <v>32580</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="34" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A34" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1334,7 +1391,7 @@
         <v>32585</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="35" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A35" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1360,7 +1417,7 @@
         <v>32680</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="36" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A36" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1386,7 +1443,7 @@
         <v>32670</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="37" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A37" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1412,7 +1469,7 @@
         <v>32695</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="38" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A38" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1438,7 +1495,7 @@
         <v>32690</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="39" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A39" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1464,7 +1521,7 @@
         <v>32700</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="40" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A40" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1490,7 +1547,7 @@
         <v>32740</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="41" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A41" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1516,7 +1573,7 @@
         <v>32720</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="42" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A42" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1542,7 +1599,7 @@
         <v>32740</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="43" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A43" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1568,7 +1625,7 @@
         <v>32765</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="44" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A44" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1594,7 +1651,7 @@
         <v>32810</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="45" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A45" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1620,7 +1677,7 @@
         <v>32805</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="46" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A46" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1646,7 +1703,7 @@
         <v>32805</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="47" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A47" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1672,7 +1729,7 @@
         <v>32815</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="48" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A48" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1698,7 +1755,7 @@
         <v>32845</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="49" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A49" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1724,7 +1781,7 @@
         <v>32865</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="50" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A50" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1750,7 +1807,7 @@
         <v>32935</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="51" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A51" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1776,7 +1833,7 @@
         <v>32935</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="52" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A52" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1802,7 +1859,7 @@
         <v>32950</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="53" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A53" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1828,7 +1885,7 @@
         <v>32935</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="54" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A54" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1854,7 +1911,7 @@
         <v>33420</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="55" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A55" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1880,7 +1937,7 @@
         <v>33430</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="56" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A56" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1906,7 +1963,7 @@
         <v>33420</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="57" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A57" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1932,7 +1989,7 @@
         <v>33435</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="58" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A58" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1958,7 +2015,7 @@
         <v>33435</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="59" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A59" t="n" s="1">
         <v>2011</v>
       </c>
@@ -1984,7 +2041,7 @@
         <v>33480</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="60" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A60" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2010,7 +2067,7 @@
         <v>33515</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="61" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A61" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2036,7 +2093,7 @@
         <v>33540</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="62" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A62" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2062,7 +2119,7 @@
         <v>33560</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="63" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A63" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2088,7 +2145,7 @@
         <v>33585</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="64" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A64" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2114,7 +2171,7 @@
         <v>33595</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="65" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A65" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2140,7 +2197,7 @@
         <v>33660</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="66" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A66" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2166,7 +2223,7 @@
         <v>33685</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="67" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A67" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2192,7 +2249,7 @@
         <v>33675</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="68" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A68" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2218,7 +2275,7 @@
         <v>33660</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="69" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A69" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2244,7 +2301,7 @@
         <v>33725</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="70" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A70" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2270,7 +2327,7 @@
         <v>33725</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="71" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A71" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2296,7 +2353,7 @@
         <v>33800</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="72" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A72" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2322,7 +2379,7 @@
         <v>33825</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="73" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A73" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2348,7 +2405,7 @@
         <v>33780</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="74" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A74" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2374,7 +2431,7 @@
         <v>33865</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="75" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A75" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2400,7 +2457,7 @@
         <v>33890</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="76" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A76" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2426,7 +2483,7 @@
         <v>33890</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="77" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A77" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2452,7 +2509,7 @@
         <v>33890</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="78" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A78" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2478,7 +2535,7 @@
         <v>33900</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="79" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A79" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2504,7 +2561,7 @@
         <v>33995</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="80" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A80" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2530,7 +2587,7 @@
         <v>34005</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="81" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A81" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2556,7 +2613,7 @@
         <v>34005</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="82" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A82" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2582,7 +2639,7 @@
         <v>34010</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="83" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A83" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2608,7 +2665,7 @@
         <v>33995</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="84" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A84" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2634,7 +2691,7 @@
         <v>34020</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="85" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A85" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2660,7 +2717,7 @@
         <v>34120</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="86" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A86" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2686,7 +2743,7 @@
         <v>34110</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="87" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A87" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2712,7 +2769,7 @@
         <v>34135</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="88" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A88" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2738,7 +2795,7 @@
         <v>34140</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="89" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A89" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2764,7 +2821,7 @@
         <v>34180</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="90" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A90" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2790,7 +2847,7 @@
         <v>34160</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="91" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A91" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2816,7 +2873,7 @@
         <v>34205</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="92" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A92" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2842,7 +2899,7 @@
         <v>34250</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="93" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A93" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2868,7 +2925,7 @@
         <v>34245</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="94" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A94" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2894,7 +2951,7 @@
         <v>34255</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="95" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A95" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2920,7 +2977,7 @@
         <v>34305</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="96" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A96" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2946,7 +3003,7 @@
         <v>34375</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="97" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A97" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2972,7 +3029,7 @@
         <v>34375</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="98" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A98" t="n" s="1">
         <v>2011</v>
       </c>
@@ -2998,7 +3055,7 @@
         <v>34390</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="99" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A99" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3024,7 +3081,7 @@
         <v>34375</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="100" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A100" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3050,7 +3107,7 @@
         <v>34860</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="101" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A101" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3076,7 +3133,7 @@
         <v>34870</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="102" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A102" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3102,7 +3159,7 @@
         <v>34860</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="103" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A103" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3128,7 +3185,7 @@
         <v>34875</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="104" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A104" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3154,7 +3211,7 @@
         <v>34875</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="105" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A105" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3180,7 +3237,7 @@
         <v>34920</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="106" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A106" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3206,7 +3263,7 @@
         <v>34955</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="107" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A107" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3232,7 +3289,7 @@
         <v>34980</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="108" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A108" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3258,7 +3315,7 @@
         <v>35000</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="109" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A109" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3284,7 +3341,7 @@
         <v>35025</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="110" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A110" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3310,7 +3367,7 @@
         <v>35035</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="111" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A111" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3336,7 +3393,7 @@
         <v>35100</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="112" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A112" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3362,7 +3419,7 @@
         <v>35125</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="113" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A113" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3388,7 +3445,7 @@
         <v>35170</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="114" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A114" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3414,7 +3471,7 @@
         <v>35115</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="115" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A115" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3440,7 +3497,7 @@
         <v>35100</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="116" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A116" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3466,7 +3523,7 @@
         <v>35165</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="117" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A117" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3492,7 +3549,7 @@
         <v>35165</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="118" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A118" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3518,7 +3575,7 @@
         <v>35165</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="119" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A119" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3544,7 +3601,7 @@
         <v>35240</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="120" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A120" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3570,7 +3627,7 @@
         <v>35220</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="121" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A121" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3596,7 +3653,7 @@
         <v>35265</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="122" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A122" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3622,7 +3679,7 @@
         <v>35265</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="123" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A123" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3648,7 +3705,7 @@
         <v>35305</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="124" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A124" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3674,7 +3731,7 @@
         <v>35290</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="125" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A125" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3700,7 +3757,7 @@
         <v>35390</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="126" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A126" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3726,7 +3783,7 @@
         <v>35330</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="127" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A127" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3752,7 +3809,7 @@
         <v>35330</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="128" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A128" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3778,7 +3835,7 @@
         <v>35340</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="129" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A129" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3804,7 +3861,7 @@
         <v>35435</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="130" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A130" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3830,7 +3887,7 @@
         <v>35445</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="131" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A131" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3856,7 +3913,7 @@
         <v>35450</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="132" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A132" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3882,7 +3939,7 @@
         <v>35435</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="133" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A133" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3908,7 +3965,7 @@
         <v>35460</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="134" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A134" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3934,7 +3991,7 @@
         <v>35465</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="135" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A135" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3960,7 +4017,7 @@
         <v>35560</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="136" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A136" t="n" s="1">
         <v>2011</v>
       </c>
@@ -3986,7 +4043,7 @@
         <v>35550</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="137" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A137" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4012,7 +4069,7 @@
         <v>35575</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="138" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A138" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4038,7 +4095,7 @@
         <v>35570</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="139" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A139" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4064,7 +4121,7 @@
         <v>35580</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="140" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A140" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4090,7 +4147,7 @@
         <v>35620</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="141" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A141" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4116,7 +4173,7 @@
         <v>35600</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="142" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A142" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4142,7 +4199,7 @@
         <v>35620</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="143" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A143" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4168,7 +4225,7 @@
         <v>35645</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="144" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A144" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4194,7 +4251,7 @@
         <v>35690</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="145" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A145" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4220,7 +4277,7 @@
         <v>35685</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="146" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A146" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4246,7 +4303,7 @@
         <v>35685</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="147" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A147" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4272,7 +4329,7 @@
         <v>35695</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="148" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A148" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4298,7 +4355,7 @@
         <v>35745</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="149" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A149" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4324,7 +4381,7 @@
         <v>35725</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="150" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A150" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4350,7 +4407,7 @@
         <v>35815</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="151" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A151" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4376,7 +4433,7 @@
         <v>35815</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="152" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A152" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4402,7 +4459,7 @@
         <v>35830</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="153" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A153" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4428,7 +4485,7 @@
         <v>35815</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="154" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A154" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4454,7 +4511,7 @@
         <v>36300</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="155" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A155" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4480,7 +4537,7 @@
         <v>36310</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="156" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A156" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4506,7 +4563,7 @@
         <v>36300</v>
       </c>
     </row>
-    <row r="157" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="157" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A157" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4532,7 +4589,7 @@
         <v>36315</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="158" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A158" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4558,7 +4615,7 @@
         <v>36315</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="159" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A159" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4584,7 +4641,7 @@
         <v>36360</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="160" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A160" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4610,7 +4667,7 @@
         <v>36395</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="161" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A161" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4636,7 +4693,7 @@
         <v>36420</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="162" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A162" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4662,7 +4719,7 @@
         <v>36440</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="163" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A163" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4688,7 +4745,7 @@
         <v>36465</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="164" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A164" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4714,7 +4771,7 @@
         <v>36475</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="165" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A165" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4740,7 +4797,7 @@
         <v>36540</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="166" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A166" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4766,7 +4823,7 @@
         <v>36565</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="167" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A167" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4792,7 +4849,7 @@
         <v>36555</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="168" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A168" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4818,7 +4875,7 @@
         <v>36540</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="169" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A169" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4844,7 +4901,7 @@
         <v>36605</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="170" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A170" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4870,7 +4927,7 @@
         <v>36605</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="171" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A171" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4896,7 +4953,7 @@
         <v>36680</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="172" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A172" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4922,7 +4979,7 @@
         <v>36660</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="173" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A173" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4948,7 +5005,7 @@
         <v>36705</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="174" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A174" t="n" s="1">
         <v>2011</v>
       </c>
@@ -4974,7 +5031,7 @@
         <v>36745</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="175" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A175" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5000,7 +5057,7 @@
         <v>36730</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="176" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A176" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5026,7 +5083,7 @@
         <v>36770</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="177" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A177" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5052,7 +5109,7 @@
         <v>36770</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="178" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A178" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5078,7 +5135,7 @@
         <v>36770</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="179" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A179" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5104,7 +5161,7 @@
         <v>36780</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="180" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A180" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5130,7 +5187,7 @@
         <v>36875</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="181" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A181" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5156,7 +5213,7 @@
         <v>36885</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="182" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A182" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5182,7 +5239,7 @@
         <v>36885</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="183" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A183" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5208,7 +5265,7 @@
         <v>36890</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="184" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A184" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5234,7 +5291,7 @@
         <v>36875</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="185" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A185" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5260,7 +5317,7 @@
         <v>36900</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="186" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A186" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5286,7 +5343,7 @@
         <v>36905</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="187" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A187" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5312,7 +5369,7 @@
         <v>37000</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="188" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A188" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5338,7 +5395,7 @@
         <v>36990</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="189" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A189" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5364,7 +5421,7 @@
         <v>37015</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="190" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A190" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5390,7 +5447,7 @@
         <v>37010</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="191" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A191" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5416,7 +5473,7 @@
         <v>37020</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="192" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A192" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5442,7 +5499,7 @@
         <v>37060</v>
       </c>
     </row>
-    <row r="193" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="193" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A193" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5468,7 +5525,7 @@
         <v>37040</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="194" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A194" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5494,7 +5551,7 @@
         <v>37060</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="195" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A195" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5520,7 +5577,7 @@
         <v>37085</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="196" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A196" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5546,7 +5603,7 @@
         <v>37130</v>
       </c>
     </row>
-    <row r="197" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="197" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A197" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5572,7 +5629,7 @@
         <v>37125</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="198" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A198" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5598,7 +5655,7 @@
         <v>37125</v>
       </c>
     </row>
-    <row r="199" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="199" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A199" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5624,7 +5681,7 @@
         <v>37135</v>
       </c>
     </row>
-    <row r="200" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="200" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A200" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5650,7 +5707,7 @@
         <v>37185</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="201" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A201" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5676,7 +5733,7 @@
         <v>37165</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="202" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A202" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5702,7 +5759,7 @@
         <v>37255</v>
       </c>
     </row>
-    <row r="203" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="203" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A203" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5728,7 +5785,7 @@
         <v>37255</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="204" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A204" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5754,7 +5811,7 @@
         <v>37270</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="205" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A205" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5780,7 +5837,7 @@
         <v>37255</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="206" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A206" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5806,7 +5863,7 @@
         <v>37740</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="207" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A207" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5832,7 +5889,7 @@
         <v>37750</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="208" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A208" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5858,7 +5915,7 @@
         <v>37740</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="209" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A209" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5884,7 +5941,7 @@
         <v>37755</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="210" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A210" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5910,7 +5967,7 @@
         <v>37755</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="211" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A211" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5936,7 +5993,7 @@
         <v>37800</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="212" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A212" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5962,7 +6019,7 @@
         <v>37835</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="213" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A213" t="n" s="1">
         <v>2011</v>
       </c>
@@ -5988,7 +6045,7 @@
         <v>37860</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="214" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A214" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6014,7 +6071,7 @@
         <v>37880</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="215" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A215" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6040,7 +6097,7 @@
         <v>37905</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="216" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A216" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6066,7 +6123,7 @@
         <v>37915</v>
       </c>
     </row>
-    <row r="217" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="217" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A217" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6092,7 +6149,7 @@
         <v>37980</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="218" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A218" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6118,7 +6175,7 @@
         <v>38005</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="219" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A219" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6144,7 +6201,7 @@
         <v>37995</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="220" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A220" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6170,7 +6227,7 @@
         <v>37980</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="221" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A221" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6196,7 +6253,7 @@
         <v>38045</v>
       </c>
     </row>
-    <row r="222" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="222" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A222" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6222,7 +6279,7 @@
         <v>38045</v>
       </c>
     </row>
-    <row r="223" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="223" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A223" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6248,7 +6305,7 @@
         <v>38045</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="224" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A224" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6274,7 +6331,7 @@
         <v>38120</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="225" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A225" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6300,7 +6357,7 @@
         <v>38145</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="226" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A226" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6326,7 +6383,7 @@
         <v>38100</v>
       </c>
     </row>
-    <row r="227" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="227" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A227" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6352,7 +6409,7 @@
         <v>38145</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="228" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A228" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6378,7 +6435,7 @@
         <v>38185</v>
       </c>
     </row>
-    <row r="229" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="229" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A229" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6404,7 +6461,7 @@
         <v>38170</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="230" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A230" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6430,7 +6487,7 @@
         <v>38210</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="231" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A231" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6456,7 +6513,7 @@
         <v>38210</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="232" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A232" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6482,7 +6539,7 @@
         <v>38210</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="233" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A233" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6508,7 +6565,7 @@
         <v>38220</v>
       </c>
     </row>
-    <row r="234" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="234" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A234" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6534,7 +6591,7 @@
         <v>38315</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="235" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A235" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6560,7 +6617,7 @@
         <v>38325</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="236" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A236" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6586,7 +6643,7 @@
         <v>38325</v>
       </c>
     </row>
-    <row r="237" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="237" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A237" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6612,7 +6669,7 @@
         <v>38330</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="238" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A238" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6638,7 +6695,7 @@
         <v>38315</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="239" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A239" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6664,7 +6721,7 @@
         <v>38340</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="240" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A240" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6690,7 +6747,7 @@
         <v>38345</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="241" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A241" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6716,7 +6773,7 @@
         <v>38440</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="242" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A242" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6742,7 +6799,7 @@
         <v>38430</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="243" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A243" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6768,7 +6825,7 @@
         <v>38455</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="244" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A244" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6794,7 +6851,7 @@
         <v>38450</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="245" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A245" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6820,7 +6877,7 @@
         <v>38460</v>
       </c>
     </row>
-    <row r="246" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="246" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A246" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6846,7 +6903,7 @@
         <v>38500</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="247" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A247" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6872,7 +6929,7 @@
         <v>38480</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="248" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A248" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6898,7 +6955,7 @@
         <v>38500</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="249" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A249" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6924,7 +6981,7 @@
         <v>38525</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="250" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A250" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6950,7 +7007,7 @@
         <v>38570</v>
       </c>
     </row>
-    <row r="251" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="251" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A251" t="n" s="1">
         <v>2011</v>
       </c>
@@ -6976,7 +7033,7 @@
         <v>38565</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="252" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A252" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7002,7 +7059,7 @@
         <v>38565</v>
       </c>
     </row>
-    <row r="253" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="253" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A253" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7028,7 +7085,7 @@
         <v>38575</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="254" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A254" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7054,7 +7111,7 @@
         <v>38625</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="255" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A255" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7080,7 +7137,7 @@
         <v>38605</v>
       </c>
     </row>
-    <row r="256" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="256" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A256" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7106,7 +7163,7 @@
         <v>38695</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="257" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A257" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7132,7 +7189,7 @@
         <v>38695</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="258" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A258" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7158,7 +7215,7 @@
         <v>38710</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="259" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A259" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7184,7 +7241,7 @@
         <v>38695</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="260" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A260" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7210,7 +7267,7 @@
         <v>39180</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="261" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A261" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7236,7 +7293,7 @@
         <v>39195</v>
       </c>
     </row>
-    <row r="262" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="262" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A262" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7262,7 +7319,7 @@
         <v>39195</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="263" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A263" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7288,7 +7345,7 @@
         <v>39190</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="264" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A264" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7314,7 +7371,7 @@
         <v>39180</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="265" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A265" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7340,7 +7397,7 @@
         <v>39275</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="266" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A266" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7366,7 +7423,7 @@
         <v>39320</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="267" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A267" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7392,7 +7449,7 @@
         <v>39355</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="268" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A268" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7418,7 +7475,7 @@
         <v>39420</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="269" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A269" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7444,7 +7501,7 @@
         <v>39445</v>
       </c>
     </row>
-    <row r="270" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="270" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A270" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7470,7 +7527,7 @@
         <v>39490</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="271" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A271" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7496,7 +7553,7 @@
         <v>39435</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="272" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A272" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7522,7 +7579,7 @@
         <v>39420</v>
       </c>
     </row>
-    <row r="273" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="273" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A273" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7548,7 +7605,7 @@
         <v>39485</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="274" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A274" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7574,7 +7631,7 @@
         <v>39560</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="275" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A275" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7600,7 +7657,7 @@
         <v>39540</v>
       </c>
     </row>
-    <row r="276" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="276" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A276" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7626,7 +7683,7 @@
         <v>39585</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="277" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A277" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7652,7 +7709,7 @@
         <v>39625</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="278" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A278" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7678,7 +7735,7 @@
         <v>39630</v>
       </c>
     </row>
-    <row r="279" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="279" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A279" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7704,7 +7761,7 @@
         <v>39710</v>
       </c>
     </row>
-    <row r="280" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="280" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A280" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7730,7 +7787,7 @@
         <v>39650</v>
       </c>
     </row>
-    <row r="281" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="281" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A281" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7756,7 +7813,7 @@
         <v>39650</v>
       </c>
     </row>
-    <row r="282" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="282" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A282" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7782,7 +7839,7 @@
         <v>39660</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="283" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A283" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7808,7 +7865,7 @@
         <v>39755</v>
       </c>
     </row>
-    <row r="284" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="284" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A284" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7834,7 +7891,7 @@
         <v>39745</v>
       </c>
     </row>
-    <row r="285" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="285" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A285" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7860,7 +7917,7 @@
         <v>39765</v>
       </c>
     </row>
-    <row r="286" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="286" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A286" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7886,7 +7943,7 @@
         <v>39770</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="287" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A287" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7912,7 +7969,7 @@
         <v>39755</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="288" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A288" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7938,7 +7995,7 @@
         <v>39780</v>
       </c>
     </row>
-    <row r="289" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="289" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A289" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7964,7 +8021,7 @@
         <v>39880</v>
       </c>
     </row>
-    <row r="290" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="290" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A290" t="n" s="1">
         <v>2011</v>
       </c>
@@ -7990,7 +8047,7 @@
         <v>39870</v>
       </c>
     </row>
-    <row r="291" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="291" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A291" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8016,7 +8073,7 @@
         <v>39895</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="292" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A292" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8042,7 +8099,7 @@
         <v>39900</v>
       </c>
     </row>
-    <row r="293" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="293" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A293" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8068,7 +8125,7 @@
         <v>39940</v>
       </c>
     </row>
-    <row r="294" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="294" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A294" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8094,7 +8151,7 @@
         <v>39920</v>
       </c>
     </row>
-    <row r="295" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="295" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A295" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8120,7 +8177,7 @@
         <v>39965</v>
       </c>
     </row>
-    <row r="296" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="296" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A296" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8146,7 +8203,7 @@
         <v>40010</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="297" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A297" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8172,7 +8229,7 @@
         <v>40005</v>
       </c>
     </row>
-    <row r="298" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="298" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A298" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8198,7 +8255,7 @@
         <v>40015</v>
       </c>
     </row>
-    <row r="299" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="299" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A299" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8224,7 +8281,7 @@
         <v>40065</v>
       </c>
     </row>
-    <row r="300" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="300" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A300" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8250,7 +8307,7 @@
         <v>40135</v>
       </c>
     </row>
-    <row r="301" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="301" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A301" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8276,7 +8333,7 @@
         <v>40135</v>
       </c>
     </row>
-    <row r="302" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="302" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A302" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8302,7 +8359,7 @@
         <v>40150</v>
       </c>
     </row>
-    <row r="303" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="303" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A303" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8328,7 +8385,7 @@
         <v>40135</v>
       </c>
     </row>
-    <row r="304" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="304" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A304" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8354,7 +8411,7 @@
         <v>40620</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="305" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A305" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8380,7 +8437,7 @@
         <v>40630</v>
       </c>
     </row>
-    <row r="306" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="306" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A306" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8406,7 +8463,7 @@
         <v>40620</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="307" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A307" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8432,7 +8489,7 @@
         <v>40635</v>
       </c>
     </row>
-    <row r="308" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="308" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A308" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8458,7 +8515,7 @@
         <v>40635</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="309" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A309" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8484,7 +8541,7 @@
         <v>40715</v>
       </c>
     </row>
-    <row r="310" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="310" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A310" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8510,7 +8567,7 @@
         <v>40760</v>
       </c>
     </row>
-    <row r="311" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="311" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A311" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8536,7 +8593,7 @@
         <v>40785</v>
       </c>
     </row>
-    <row r="312" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="312" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A312" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8562,7 +8619,7 @@
         <v>40795</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="313" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A313" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8588,7 +8645,7 @@
         <v>40860</v>
       </c>
     </row>
-    <row r="314" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="314" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A314" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8614,7 +8671,7 @@
         <v>40885</v>
       </c>
     </row>
-    <row r="315" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="315" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A315" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8640,7 +8697,7 @@
         <v>40875</v>
       </c>
     </row>
-    <row r="316" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="316" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A316" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8666,7 +8723,7 @@
         <v>40860</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="317" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A317" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8692,7 +8749,7 @@
         <v>40925</v>
       </c>
     </row>
-    <row r="318" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="318" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A318" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8718,7 +8775,7 @@
         <v>40925</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="319" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A319" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8744,7 +8801,7 @@
         <v>40925</v>
       </c>
     </row>
-    <row r="320" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="320" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A320" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8770,7 +8827,7 @@
         <v>41000</v>
       </c>
     </row>
-    <row r="321" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="321" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A321" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8796,7 +8853,7 @@
         <v>40980</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="322" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A322" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8822,7 +8879,7 @@
         <v>41025</v>
       </c>
     </row>
-    <row r="323" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="323" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A323" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8848,7 +8905,7 @@
         <v>41025</v>
       </c>
     </row>
-    <row r="324" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="324" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A324" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8874,7 +8931,7 @@
         <v>41065</v>
       </c>
     </row>
-    <row r="325" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="325" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A325" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8900,7 +8957,7 @@
         <v>41050</v>
       </c>
     </row>
-    <row r="326" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="326" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A326" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8926,7 +8983,7 @@
         <v>41090</v>
       </c>
     </row>
-    <row r="327" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="327" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A327" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8952,7 +9009,7 @@
         <v>41090</v>
       </c>
     </row>
-    <row r="328" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="328" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A328" t="n" s="1">
         <v>2011</v>
       </c>
@@ -8978,7 +9035,7 @@
         <v>41090</v>
       </c>
     </row>
-    <row r="329" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="329" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A329" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9004,7 +9061,7 @@
         <v>41100</v>
       </c>
     </row>
-    <row r="330" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="330" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A330" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9030,7 +9087,7 @@
         <v>41195</v>
       </c>
     </row>
-    <row r="331" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="331" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A331" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9056,7 +9113,7 @@
         <v>41205</v>
       </c>
     </row>
-    <row r="332" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="332" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A332" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9082,7 +9139,7 @@
         <v>41205</v>
       </c>
     </row>
-    <row r="333" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="333" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A333" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9108,7 +9165,7 @@
         <v>41210</v>
       </c>
     </row>
-    <row r="334" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="334" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A334" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9134,7 +9191,7 @@
         <v>41195</v>
       </c>
     </row>
-    <row r="335" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="335" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A335" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9160,7 +9217,7 @@
         <v>41220</v>
       </c>
     </row>
-    <row r="336" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="336" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A336" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9186,7 +9243,7 @@
         <v>41225</v>
       </c>
     </row>
-    <row r="337" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="337" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A337" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9212,7 +9269,7 @@
         <v>41320</v>
       </c>
     </row>
-    <row r="338" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="338" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A338" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9238,7 +9295,7 @@
         <v>41310</v>
       </c>
     </row>
-    <row r="339" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="339" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A339" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9264,7 +9321,7 @@
         <v>41335</v>
       </c>
     </row>
-    <row r="340" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="340" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A340" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9290,7 +9347,7 @@
         <v>41330</v>
       </c>
     </row>
-    <row r="341" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="341" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A341" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9316,7 +9373,7 @@
         <v>41340</v>
       </c>
     </row>
-    <row r="342" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="342" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A342" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9342,7 +9399,7 @@
         <v>41380</v>
       </c>
     </row>
-    <row r="343" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="343" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A343" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9368,7 +9425,7 @@
         <v>41360</v>
       </c>
     </row>
-    <row r="344" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="344" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A344" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9394,7 +9451,7 @@
         <v>41380</v>
       </c>
     </row>
-    <row r="345" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="345" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A345" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9420,7 +9477,7 @@
         <v>41405</v>
       </c>
     </row>
-    <row r="346" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="346" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A346" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9446,7 +9503,7 @@
         <v>41450</v>
       </c>
     </row>
-    <row r="347" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="347" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A347" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9472,7 +9529,7 @@
         <v>41445</v>
       </c>
     </row>
-    <row r="348" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="348" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A348" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9498,7 +9555,7 @@
         <v>41445</v>
       </c>
     </row>
-    <row r="349" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="349" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A349" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9524,7 +9581,7 @@
         <v>41455</v>
       </c>
     </row>
-    <row r="350" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="350" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A350" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9550,7 +9607,7 @@
         <v>41505</v>
       </c>
     </row>
-    <row r="351" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="351" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A351" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9576,7 +9633,7 @@
         <v>41485</v>
       </c>
     </row>
-    <row r="352" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="352" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A352" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9602,7 +9659,7 @@
         <v>41575</v>
       </c>
     </row>
-    <row r="353" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="353" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A353" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9628,7 +9685,7 @@
         <v>41575</v>
       </c>
     </row>
-    <row r="354" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="354" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A354" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9654,7 +9711,7 @@
         <v>41590</v>
       </c>
     </row>
-    <row r="355" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="355" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A355" t="n" s="1">
         <v>2011</v>
       </c>
@@ -9699,7 +9756,7 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:10" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="1" spans="1:10" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A1" t="s">
         <v>58</v>
       </c>
@@ -9731,7 +9788,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="2" spans="1:10" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A2">
         <v>35</v>
       </c>
@@ -9782,7 +9839,7 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="1" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A1" t="s" s="1">
         <v>36</v>
       </c>
@@ -9808,7 +9865,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="2" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A2" t="s" s="1">
         <v>24</v>
       </c>
@@ -9834,7 +9891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="3" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A3" t="s" s="1">
         <v>9</v>
       </c>
@@ -9860,7 +9917,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="4" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A4" t="s" s="1">
         <v>16</v>
       </c>
@@ -9886,7 +9943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="5" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A5" t="s" s="1">
         <v>25</v>
       </c>
@@ -9912,7 +9969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="6" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A6" t="s" s="1">
         <v>22</v>
       </c>
@@ -9938,7 +9995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="7" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A7" t="s" s="1">
         <v>17</v>
       </c>
@@ -9964,7 +10021,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="8" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A8" t="s" s="1">
         <v>10</v>
       </c>
@@ -9990,7 +10047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="9" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A9" t="s" s="1">
         <v>20</v>
       </c>
@@ -10016,7 +10073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="10" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A10" t="s" s="1">
         <v>11</v>
       </c>
@@ -10042,7 +10099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="11" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A11" t="s" s="1">
         <v>29</v>
       </c>
@@ -10068,7 +10125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="12" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A12" t="s" s="1">
         <v>23</v>
       </c>
@@ -10094,7 +10151,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="13" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A13" t="s" s="1">
         <v>14</v>
       </c>
@@ -10120,7 +10177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="14" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A14" t="s" s="1">
         <v>27</v>
       </c>
@@ -10146,7 +10203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="15" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A15" t="s" s="1">
         <v>13</v>
       </c>
@@ -10172,7 +10229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="16" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A16" t="s" s="1">
         <v>44</v>
       </c>
@@ -10198,7 +10255,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="17" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A17" t="s" s="1">
         <v>28</v>
       </c>
@@ -10224,7 +10281,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="18" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A18" t="s" s="1">
         <v>8</v>
       </c>
@@ -10250,7 +10307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="19" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A19" t="s" s="1">
         <v>26</v>
       </c>
@@ -10276,7 +10333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="20" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A20" t="s" s="1">
         <v>15</v>
       </c>
@@ -10302,7 +10359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="21" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A21" t="s" s="1">
         <v>18</v>
       </c>
@@ -10328,7 +10385,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="22" spans="1:8" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
       <c r="A22" t="s" s="1">
         <v>21</v>
       </c>
@@ -10354,7 +10411,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="false" customFormat="false" ht="12.8" customHeight="false" collapsed="false" outlineLevel="0">
+    <row r="23" spans="1:8" hidden="false" outlineLevel="0" ht="12.8" customHeight="false" collapsed="false" customFormat="false">
       <c r="A23" t="s" s="0">
         <v>12</v>
       </c>
@@ -10399,156 +10456,156 @@
   <dimension ref="A1:E9"/>
   <sheetFormatPr defaultColWidth="10.58203125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A1" t="s" s="1">
-        <v>45</v>
-      </c>
-      <c r="B1" t="s" s="1">
+    <row r="1" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2">
+        <v>5480</v>
+      </c>
+      <c r="D2">
         <v>46</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>47</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>48</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A2" t="s" s="1">
-        <v>50</v>
-      </c>
-      <c r="B2" t="s" s="3">
-        <v>8</v>
-      </c>
-      <c r="C2" t="n" s="3">
-        <v>5480</v>
-      </c>
-      <c r="D2" t="n" s="4">
-        <v>46</v>
-      </c>
-      <c r="E2" t="n" s="4">
+      <c r="E2">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A3" t="s" s="1">
-        <v>51</v>
-      </c>
-      <c r="B3" t="s" s="3">
-        <v>14</v>
-      </c>
-      <c r="C3" t="n" s="3">
+    <row r="3" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" t="n" s="1">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
-      <c r="E3" t="n" s="1">
+    </row>
+    <row r="4" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A4" t="s" s="1">
-        <v>52</v>
-      </c>
-      <c r="B4" t="s" s="3">
-        <v>13</v>
-      </c>
-      <c r="C4" t="n" s="3">
+    <row r="5" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5">
         <v>0</v>
       </c>
-      <c r="D4" t="n" s="1">
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="E4" t="n" s="1">
+    </row>
+    <row r="6" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A5" t="s" s="1">
-        <v>53</v>
-      </c>
-      <c r="B5" t="s" s="3">
-        <v>11</v>
-      </c>
-      <c r="C5" t="n" s="3">
+    <row r="7" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7">
         <v>0</v>
       </c>
-      <c r="D5" t="n" s="1">
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
-      <c r="E5" t="n" s="1">
+    </row>
+    <row r="8" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A6" t="s" s="1">
-        <v>54</v>
-      </c>
-      <c r="B6" t="s" s="3">
-        <v>8</v>
-      </c>
-      <c r="C6" t="n" s="3">
+    <row r="9" spans="1:5" hidden="false" outlineLevel="0" ht="15" customHeight="false" collapsed="false" customFormat="false">
+      <c r="A9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9">
         <v>0</v>
       </c>
-      <c r="D6" t="n" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A7" t="s" s="1">
-        <v>55</v>
-      </c>
-      <c r="B7" t="s" s="3">
-        <v>10</v>
-      </c>
-      <c r="C7" t="n" s="3">
+      <c r="D9">
         <v>0</v>
       </c>
-      <c r="D7" t="n" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A8" t="s" s="1">
-        <v>56</v>
-      </c>
-      <c r="B8" t="s" s="3">
-        <v>12</v>
-      </c>
-      <c r="C8" t="n" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" hidden="false" customFormat="false" ht="15" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A9" t="s" s="1">
-        <v>57</v>
-      </c>
-      <c r="B9" t="s" s="3">
-        <v>8</v>
-      </c>
-      <c r="C9" t="n" s="3">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n" s="1">
+      <c r="E9">
         <v>1</v>
       </c>
     </row>

--- a/INSTANCES/instances_literature_xlsx/A_MTN_1/354FL_8A_9.xlsx
+++ b/INSTANCES/instances_literature_xlsx/A_MTN_1/354FL_8A_9.xlsx
@@ -9848,10 +9848,10 @@
         <v>480</v>
       </c>
       <c r="D2">
-        <v>50</v>
+        <v>78.0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>12.0</v>
       </c>
       <c r="F2">
         <v>7</v>
@@ -9910,7 +9910,7 @@
         <v>24</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -9951,10 +9951,10 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -9971,7 +9971,7 @@
         <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -9988,25 +9988,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -10032,7 +10032,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -10073,10 +10073,10 @@
         <v>5480</v>
       </c>
       <c r="D2">
-        <v>46</v>
+        <v>72.0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
